--- a/data/trans_dic/P1402-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1402-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,67</t>
+          <t>3,34; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,28</t>
+          <t>2,3; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,81</t>
+          <t>5,01; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,7</t>
+          <t>7,11; 11,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,29</t>
+          <t>0,86; 3,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,33</t>
+          <t>1,65; 6,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,59</t>
+          <t>2,72; 7,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,66</t>
+          <t>2,27; 4,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,72</t>
+          <t>2,65; 5,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,51</t>
+          <t>2,58; 5,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,09</t>
+          <t>4,66; 8,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,77</t>
+          <t>5,11; 7,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,2</t>
+          <t>3,01; 7,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,92</t>
+          <t>3,32; 8,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,94</t>
+          <t>4,92; 10,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,61</t>
+          <t>6,3; 11,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,52</t>
+          <t>0,9; 4,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,26</t>
+          <t>1,26; 5,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,68</t>
+          <t>1,48; 5,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,72</t>
+          <t>1,5; 3,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,16</t>
+          <t>2,47; 5,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,99</t>
+          <t>2,9; 6,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,2</t>
+          <t>3,61; 6,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,72</t>
+          <t>4,52; 7,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,9</t>
+          <t>3,55; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 14,15</t>
+          <t>9,28; 14,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 13,31</t>
+          <t>7,81; 13,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 13,07</t>
+          <t>8,89; 14,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 13,16</t>
+          <t>4,48; 13,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,63</t>
+          <t>3,76; 9,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,86</t>
+          <t>2,75; 11,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 14,28</t>
+          <t>6,88; 13,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,61</t>
+          <t>4,34; 7,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,07</t>
+          <t>7,94; 12,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,5</t>
+          <t>7,36; 11,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,05</t>
+          <t>9,08; 13,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,16</t>
+          <t>6,2; 9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 10,81</t>
+          <t>7,3; 10,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,52</t>
+          <t>8,26; 11,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,94</t>
+          <t>9,94; 13,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,43</t>
+          <t>3,25; 6,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,43</t>
+          <t>4,16; 7,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,5</t>
+          <t>2,77; 5,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,5</t>
+          <t>4,81; 7,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,65</t>
+          <t>5,4; 7,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,84</t>
+          <t>6,46; 9,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,59</t>
+          <t>6,17; 8,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,47</t>
+          <t>7,98; 10,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,27 +1244,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>10,29%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,06</t>
+          <t>4,26; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,65</t>
+          <t>4,83; 9,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 14,03</t>
+          <t>8,96; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,65</t>
+          <t>6,73; 10,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,6</t>
+          <t>4,4; 8,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,72</t>
+          <t>7,43; 11,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,95</t>
+          <t>7,56; 12,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,4</t>
+          <t>9,75; 13,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,98</t>
+          <t>4,73; 7,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,28</t>
+          <t>7,02; 10,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,11</t>
+          <t>8,75; 12,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,45</t>
+          <t>9,13; 11,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,0</t>
+          <t>0,74; 5,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,75</t>
+          <t>0,39; 3,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,53</t>
+          <t>0,23; 2,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,43</t>
+          <t>9,05; 12,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,17; 16,29</t>
+          <t>12,12; 16,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 16,83</t>
+          <t>12,07; 16,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,89; 13,37</t>
+          <t>9,91; 13,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,06</t>
+          <t>7,33; 10,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,53</t>
+          <t>9,81; 13,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,56</t>
+          <t>9,83; 13,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,43</t>
+          <t>7,79; 10,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,49</t>
+          <t>4,96; 6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,43</t>
+          <t>6,65; 8,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,88; 9,77</t>
+          <t>7,91; 9,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,04</t>
+          <t>8,62; 10,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,58</t>
+          <t>5,97; 7,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,74; 9,63</t>
+          <t>7,7; 9,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,43</t>
+          <t>7,49; 9,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,16</t>
+          <t>7,26; 8,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,82</t>
+          <t>5,66; 6,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,72</t>
+          <t>7,44; 8,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 9,29</t>
+          <t>7,93; 9,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 8,81</t>
+          <t>8,16; 9,23</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59794</t>
+          <t>65938</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16142; 36342</t>
+          <t>15805; 36021</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10305; 27435</t>
+          <t>10053; 27062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21901; 46364</t>
+          <t>21483; 44757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33897; 59093</t>
+          <t>39126; 64881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2614; 13162</t>
+          <t>2628; 11988</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5175; 19901</t>
+          <t>5194; 19188</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9740; 26326</t>
+          <t>9443; 25045</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9319; 20826</t>
+          <t>11071; 23671</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21326; 44635</t>
+          <t>20705; 42306</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18494; 41442</t>
+          <t>19421; 42834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35157; 62765</t>
+          <t>36189; 64400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47312; 73978</t>
+          <t>53022; 81460</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>52002</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11000; 26425</t>
+          <t>11049; 26914</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14318; 33186</t>
+          <t>13888; 33654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18286; 37478</t>
+          <t>18554; 38833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30989; 52493</t>
+          <t>30450; 53397</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3376; 16800</t>
+          <t>3352; 17834</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4118; 17771</t>
+          <t>4244; 16986</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5520; 21131</t>
+          <t>5495; 20471</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5365; 14206</t>
+          <t>6332; 15827</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17519; 38142</t>
+          <t>18214; 37696</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22685; 45312</t>
+          <t>21925; 45509</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26945; 53968</t>
+          <t>27032; 51164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39191; 64370</t>
+          <t>40943; 65969</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51295</t>
+          <t>53992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68237</t>
+          <t>72751</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18260; 37423</t>
+          <t>19248; 38725</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56571; 89061</t>
+          <t>58412; 91599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41197; 69484</t>
+          <t>40748; 69668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18312; 87278</t>
+          <t>41869; 66029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7784; 22085</t>
+          <t>7517; 22238</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9078; 25057</t>
+          <t>9773; 24404</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4763; 18042</t>
+          <t>4571; 18670</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12134; 23830</t>
+          <t>12900; 25507</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28904; 54060</t>
+          <t>30821; 55395</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70259; 107328</t>
+          <t>70611; 109365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49490; 79095</t>
+          <t>50619; 81557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27339; 100511</t>
+          <t>59740; 88506</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>129958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>51380</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>161620</t>
+          <t>181338</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76651; 113380</t>
+          <t>76830; 111722</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84459; 125289</t>
+          <t>84577; 124972</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92327; 132385</t>
+          <t>95006; 136421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97806; 133742</t>
+          <t>112399; 149957</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23755; 45905</t>
+          <t>23201; 45131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30741; 56848</t>
+          <t>31799; 59273</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22768; 45463</t>
+          <t>22916; 46412</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24568; 63574</t>
+          <t>41441; 62557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>105467; 149354</t>
+          <t>105447; 148688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122215; 169995</t>
+          <t>124181; 174395</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125407; 169619</t>
+          <t>121956; 169210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114236; 190506</t>
+          <t>159006; 205937</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43088</t>
+          <t>48280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>86344</t>
+          <t>95399</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>129432</t>
+          <t>143679</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13731; 31743</t>
+          <t>14922; 33646</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25621; 49260</t>
+          <t>24664; 50077</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54997; 87099</t>
+          <t>55591; 86569</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33244; 55110</t>
+          <t>38081; 61580</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25093; 48886</t>
+          <t>25035; 48668</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56594; 89123</t>
+          <t>56487; 90122</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56248; 88198</t>
+          <t>55813; 89292</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64322; 104010</t>
+          <t>80901; 109474</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43286; 73399</t>
+          <t>43504; 72505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90484; 130660</t>
+          <t>89180; 130404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120240; 164600</t>
+          <t>118895; 163287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105914; 150196</t>
+          <t>127442; 161298</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>87933</t>
+          <t>96095</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>98109</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1888; 13357</t>
+          <t>1973; 13367</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1136; 10765</t>
+          <t>1122; 9398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>481; 6077</t>
+          <t>536; 6006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>112425; 155272</t>
+          <t>112959; 154765</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>135025; 180729</t>
+          <t>134464; 180459</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>131349; 182129</t>
+          <t>130548; 179479</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>75213; 101671</t>
+          <t>83573; 110793</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111836; 155577</t>
+          <t>113444; 157019</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135879; 186175</t>
+          <t>134971; 188681</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134693; 185686</t>
+          <t>134630; 185914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>76020; 104338</t>
+          <t>84185; 115662</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>325945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>261016</t>
+          <t>287873</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>559313</t>
+          <t>613818</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>160878; 212394</t>
+          <t>162122; 214061</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>225395; 288486</t>
+          <t>227395; 292993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266782; 330684</t>
+          <t>267947; 333328</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>233959; 338637</t>
+          <t>296272; 359294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>201098; 255999</t>
+          <t>201810; 258740</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>274590; 341638</t>
+          <t>273147; 340578</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>263662; 333043</t>
+          <t>264587; 334338</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>207779; 291511</t>
+          <t>263646; 313430</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>375225; 453100</t>
+          <t>376343; 458066</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>517498; 607513</t>
+          <t>518142; 611216</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>548347; 642598</t>
+          <t>548735; 644076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>483359; 611701</t>
+          <t>576823; 652896</t>
         </is>
       </c>
     </row>
